--- a/Dependencies/Sample_maps/sample_map_pooled.xlsx
+++ b/Dependencies/Sample_maps/sample_map_pooled.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Documents\MS\2026_03_15_Neurodegeneration\Sample_maps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexmaropakis/Projects/BrainDecode/Dependencies/Sample_maps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F06DAC-3721-435C-85BC-90ABAE0A14F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4907B743-1A07-574C-89ED-15405DB1A87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="830" windowWidth="18750" windowHeight="12730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="2540" windowWidth="18760" windowHeight="12740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,12 +42,6 @@
     <t>MQ</t>
   </si>
   <si>
-    <t>Sample name</t>
-  </si>
-  <si>
-    <t>Sample ID</t>
-  </si>
-  <si>
     <t>LPC</t>
   </si>
   <si>
@@ -151,6 +145,12 @@
   </si>
   <si>
     <t>S1</t>
+  </si>
+  <si>
+    <t>sample_name</t>
+  </si>
+  <si>
+    <t>sample_ID</t>
   </si>
 </sst>
 </file>
@@ -484,9 +484,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,13 +503,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -517,226 +517,226 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
